--- a/artfynd/A 1901-2021 artfynd.xlsx
+++ b/artfynd/A 1901-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1901-2021 artfynd.xlsx
+++ b/artfynd/A 1901-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>3202201</v>
       </c>
       <c r="B2" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>386426.2275329779</v>
+        <v>386426</v>
       </c>
       <c r="R2" t="n">
-        <v>6385994.462176631</v>
+        <v>6385994</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1984-08-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1984-08-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -799,12 +784,7 @@
         <v>6434154</v>
       </c>
       <c r="B3" t="n">
-        <v>100515</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102801</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>386426.2275329779</v>
+        <v>386426</v>
       </c>
       <c r="R3" t="n">
-        <v>6385994.462176631</v>
+        <v>6385994</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -865,19 +845,9 @@
           <t>1984-08-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1984-08-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 1901-2021 artfynd.xlsx
+++ b/artfynd/A 1901-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3202201</v>
       </c>
       <c r="B2" t="n">
-        <v>106169</v>
+        <v>106181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>6434154</v>
       </c>
       <c r="B3" t="n">
-        <v>102801</v>
+        <v>102812</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1901-2021 artfynd.xlsx
+++ b/artfynd/A 1901-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3202201</v>
       </c>
       <c r="B2" t="n">
-        <v>106181</v>
+        <v>106190</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>6434154</v>
       </c>
       <c r="B3" t="n">
-        <v>102812</v>
+        <v>102820</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1901-2021 artfynd.xlsx
+++ b/artfynd/A 1901-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3202201</v>
       </c>
       <c r="B2" t="n">
-        <v>106190</v>
+        <v>106202</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>6434154</v>
       </c>
       <c r="B3" t="n">
-        <v>102820</v>
+        <v>102830</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1901-2021 artfynd.xlsx
+++ b/artfynd/A 1901-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3202201</v>
       </c>
       <c r="B2" t="n">
-        <v>106202</v>
+        <v>106211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>6434154</v>
       </c>
       <c r="B3" t="n">
-        <v>102830</v>
+        <v>102836</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1901-2021 artfynd.xlsx
+++ b/artfynd/A 1901-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3202201</v>
       </c>
       <c r="B2" t="n">
-        <v>106211</v>
+        <v>106216</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>6434154</v>
       </c>
       <c r="B3" t="n">
-        <v>102836</v>
+        <v>102837</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1901-2021 artfynd.xlsx
+++ b/artfynd/A 1901-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3202201</v>
       </c>
       <c r="B2" t="n">
-        <v>106216</v>
+        <v>106244</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>6434154</v>
       </c>
       <c r="B3" t="n">
-        <v>102837</v>
+        <v>102864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1901-2021 artfynd.xlsx
+++ b/artfynd/A 1901-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3202201</v>
       </c>
       <c r="B2" t="n">
-        <v>106244</v>
+        <v>106250</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>6434154</v>
       </c>
       <c r="B3" t="n">
-        <v>102864</v>
+        <v>102870</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1901-2021 artfynd.xlsx
+++ b/artfynd/A 1901-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3202201</v>
       </c>
       <c r="B2" t="n">
-        <v>106250</v>
+        <v>106257</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>6434154</v>
       </c>
       <c r="B3" t="n">
-        <v>102870</v>
+        <v>102877</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1901-2021 artfynd.xlsx
+++ b/artfynd/A 1901-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3202201</v>
       </c>
       <c r="B2" t="n">
-        <v>106257</v>
+        <v>106261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>6434154</v>
       </c>
       <c r="B3" t="n">
-        <v>102877</v>
+        <v>102881</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 1901-2021 artfynd.xlsx
+++ b/artfynd/A 1901-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3202201</v>
       </c>
       <c r="B2" t="n">
-        <v>106261</v>
+        <v>106268</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>6434154</v>
       </c>
       <c r="B3" t="n">
-        <v>102881</v>
+        <v>102888</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
